--- a/Starting_point.xlsx
+++ b/Starting_point.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fthcn\Desktop\Vaccine_Tender_Scheduling_Problem\Julia_Files\Github\Github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A8FEE2-BE8F-4FE6-A73D-C8D61511F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{30A8FEE2-BE8F-4FE6-A73D-C8D61511F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B156796-CD29-4EB6-9C6D-38224C923425}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -153,7 +153,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="173" formatCode="0.000E+00"/>
+    <numFmt numFmtId="164" formatCode="0.000E+00"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -225,7 +225,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -510,9 +510,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942AD6D9-E2BE-4540-AD66-B6783F716305}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -523,7 +523,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,7 +534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -545,7 +545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -556,7 +556,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -567,7 +567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -578,7 +578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -589,7 +589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -600,7 +600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -611,7 +611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -622,7 +622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -633,7 +633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -663,15 +663,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86710C76-81AC-48E5-8A5F-29B3CE6BD5DC}">
   <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="8.85546875" style="2"/>
     <col min="2" max="2" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.88671875" style="2"/>
-    <col min="5" max="5" width="16.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.85546875" style="2"/>
+    <col min="5" max="5" width="16.140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -688,7 +688,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>13299464</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -722,7 +722,7 @@
         <v>12505034</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -739,7 +739,7 @@
         <v>13547121</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -756,7 +756,7 @@
         <v>6547121</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -773,7 +773,7 @@
         <v>90279149</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
@@ -790,7 +790,7 @@
         <v>180177056</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -807,7 +807,7 @@
         <v>13305452</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -824,7 +824,7 @@
         <v>8948035</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -841,7 +841,7 @@
         <v>140931564</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
@@ -858,7 +858,7 @@
         <v>17896071</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -875,7 +875,7 @@
         <v>31318125</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
@@ -892,7 +892,7 @@
         <v>53688215</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>43365104</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -926,7 +926,7 @@
         <v>40213942</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
@@ -943,7 +943,7 @@
         <v>219201481</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>34</v>
       </c>
@@ -960,7 +960,7 @@
         <v>61220888</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
@@ -977,7 +977,7 @@
         <v>84680592</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -994,7 +994,7 @@
         <v>3625021</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>13464366</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>5390769</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>10</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>56510400</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>13</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>185663042</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>13</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>13</v>
       </c>
@@ -1138,9 +1138,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFBA2FAA-95C5-423D-A8C0-3A912D67D407}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>12542</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>7598</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>14598</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1188,13 +1188,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C2B8D5-A351-43B6-AB72-03AAE787B34B}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>37210000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>2610000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>35730000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>5706000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>5777000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>3207000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>2595000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>3123000</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>5222000</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>1900000</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>14250000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>

--- a/Starting_point.xlsx
+++ b/Starting_point.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{30A8FEE2-BE8F-4FE6-A73D-C8D61511F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B156796-CD29-4EB6-9C6D-38224C923425}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{30A8FEE2-BE8F-4FE6-A73D-C8D61511F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26191373-4001-4A6D-8E83-E74EC036AF36}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14180" yWindow="520" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -244,6 +244,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -511,6 +515,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942AD6D9-E2BE-4540-AD66-B6783F716305}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1139,6 +1146,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFBA2FAA-95C5-423D-A8C0-3A912D67D407}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1191,7 +1201,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">

--- a/Starting_point.xlsx
+++ b/Starting_point.xlsx
@@ -1,34 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/horizon excursion/15 years - Initial Condition sensitivity/starts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{30A8FEE2-BE8F-4FE6-A73D-C8D61511F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26191373-4001-4A6D-8E83-E74EC036AF36}"/>
+  <xr:revisionPtr revIDLastSave="872" documentId="13_ncr:1_{30A8FEE2-BE8F-4FE6-A73D-C8D61511F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32972361-2A4C-49FE-B2B6-9A3224C8A879}"/>
   <bookViews>
-    <workbookView xWindow="14180" yWindow="520" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
     <sheet name="Q_start" sheetId="3" r:id="rId2"/>
     <sheet name="I_start" sheetId="4" r:id="rId3"/>
     <sheet name="S_start" sheetId="5" r:id="rId4"/>
+    <sheet name="Medium_Capacity" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">I_start!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Medium_Capacity!$A$2:$P$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Q_start!$A$1:$P$53</definedName>
+    <definedName name="GAVI_countries">#REF!</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="57">
   <si>
     <t>Measles</t>
   </si>
@@ -145,17 +163,72 @@
   </si>
   <si>
     <t>Antigen</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>HepB</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>DTwP</t>
+  </si>
+  <si>
+    <t>DTwP-Hib</t>
+  </si>
+  <si>
+    <t>Hexa</t>
+  </si>
+  <si>
+    <t>Centro_de</t>
+  </si>
+  <si>
+    <t>AJ_Vaccines</t>
+  </si>
+  <si>
+    <t>Bilthoven</t>
+  </si>
+  <si>
+    <t>Beijing_Institute</t>
+  </si>
+  <si>
+    <t>Haffkine_Bio</t>
+  </si>
+  <si>
+    <t>Check Sum</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Diffs</t>
+  </si>
+  <si>
+    <t>Percent of whole</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>percent share</t>
+  </si>
+  <si>
+    <t>antigen demand</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.000E+00"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,13 +254,32 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF098658"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -208,11 +300,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -221,17 +314,55 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{7E8BD9F5-B830-4B85-AC68-AF3D69635AE5}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -515,9 +646,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942AD6D9-E2BE-4540-AD66-B6783F716305}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -538,7 +666,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -549,7 +677,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -560,7 +688,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -637,7 +765,7 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -659,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -669,16 +797,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86710C76-81AC-48E5-8A5F-29B3CE6BD5DC}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="2"/>
-    <col min="2" max="2" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="8.85546875" style="2"/>
     <col min="5" max="5" width="16.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="18.42578125" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -694,463 +827,1351 @@
       <c r="E1" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <f ca="1">ROUND(F2*G2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="22">
+        <f ca="1">RANDBETWEEN(8,12)/10</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>3</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E52" ca="1" si="0">ROUND(F3*G3,0)</f>
+        <v>15959357</v>
+      </c>
+      <c r="F3">
         <v>13299464</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="G3" s="22">
+        <f t="shared" ref="G3:G52" ca="1" si="1">RANDBETWEEN(8,12)/10</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ca="1" si="0"/>
+        <v>81251234</v>
+      </c>
+      <c r="F5">
+        <v>90279149</v>
+      </c>
+      <c r="G5" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.9</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <f t="shared" ca="1" si="0"/>
+        <v>16256545</v>
+      </c>
+      <c r="F6">
+        <v>13547121</v>
+      </c>
+      <c r="G6" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <f t="shared" ca="1" si="0"/>
         <v>12505034</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="F7">
+        <v>12505034</v>
+      </c>
+      <c r="G7" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <f t="shared" ca="1" si="0"/>
+        <v>2400611</v>
+      </c>
+      <c r="F8">
+        <v>2182374</v>
+      </c>
+      <c r="G8" s="22">
+        <f ca="1">RANDBETWEEN(8,12)/10</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2">
-        <v>3</v>
-      </c>
-      <c r="E4" s="3">
-        <v>13547121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <f t="shared" ca="1" si="0"/>
+        <v>4334425</v>
+      </c>
+      <c r="F9" s="23">
+        <v>4334425</v>
+      </c>
+      <c r="G9" s="22">
+        <f ca="1">RANDBETWEEN(8,12)/10</f>
+        <v>1</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="22">
+        <f ca="1">RANDBETWEEN(8,12)/10</f>
+        <v>1.2</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <f t="shared" ca="1" si="0"/>
+        <v>30000</v>
+      </c>
+      <c r="F16" s="23">
+        <v>30000</v>
+      </c>
+      <c r="G16" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <f t="shared" ca="1" si="0"/>
+        <v>48256730</v>
+      </c>
+      <c r="F17">
+        <v>40213942</v>
+      </c>
+      <c r="G17" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2</v>
+      </c>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2</v>
+      </c>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <f t="shared" ca="1" si="0"/>
+        <v>52038125</v>
+      </c>
+      <c r="F20">
+        <v>43365104</v>
+      </c>
+      <c r="G20" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2</v>
+      </c>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <f t="shared" ca="1" si="0"/>
+        <v>46574326</v>
+      </c>
+      <c r="F22">
+        <v>42340296</v>
+      </c>
+      <c r="G22" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="O22" s="10"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <f t="shared" ca="1" si="0"/>
+        <v>263041777</v>
+      </c>
+      <c r="F23">
+        <v>219201481</v>
+      </c>
+      <c r="G23" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2</v>
+      </c>
+      <c r="O23" s="10"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <f t="shared" ca="1" si="0"/>
+        <v>73465066</v>
+      </c>
+      <c r="F24">
+        <v>61220888</v>
+      </c>
+      <c r="G24" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="O24" s="10"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="O25" s="10"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2</v>
+      </c>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="O26" s="10"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="O27" s="10"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <f t="shared" ca="1" si="0"/>
+        <v>5400000</v>
+      </c>
+      <c r="F28" s="23">
+        <v>6000000</v>
+      </c>
+      <c r="G28" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.9</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="O28" s="10"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.9</v>
+      </c>
+      <c r="J29" s="2"/>
+      <c r="O29" s="10"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2</v>
+      </c>
+      <c r="O31" s="18"/>
+      <c r="P31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <f t="shared" ca="1" si="0"/>
+        <v>198194762</v>
+      </c>
+      <c r="F32">
+        <v>180177056</v>
+      </c>
+      <c r="G32" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <f t="shared" ca="1" si="0"/>
+        <v>14635997</v>
+      </c>
+      <c r="F34">
+        <v>13305452</v>
+      </c>
+      <c r="G34" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2</v>
+      </c>
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.9</v>
+      </c>
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <f t="shared" ca="1" si="0"/>
+        <v>126838408</v>
+      </c>
+      <c r="F38">
+        <v>140931564</v>
+      </c>
+      <c r="G38" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <f t="shared" ca="1" si="0"/>
+        <v>25054500</v>
+      </c>
+      <c r="F39">
+        <v>31318125</v>
+      </c>
+      <c r="G39" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <f t="shared" ca="1" si="0"/>
+        <v>42950572</v>
+      </c>
+      <c r="F40">
+        <v>53688215</v>
+      </c>
+      <c r="G40" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <f t="shared" ca="1" si="0"/>
+        <v>17896071</v>
+      </c>
+      <c r="F41">
+        <v>17896071</v>
+      </c>
+      <c r="G41" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <f t="shared" ca="1" si="0"/>
+        <v>8948035</v>
+      </c>
+      <c r="F42">
+        <v>8948035</v>
+      </c>
+      <c r="G42" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <f t="shared" ca="1" si="0"/>
+        <v>14810803</v>
+      </c>
+      <c r="F44">
+        <v>13464366</v>
+      </c>
+      <c r="G44" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
-        <v>3</v>
-      </c>
-      <c r="E5" s="4">
-        <v>6547121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>3</v>
-      </c>
-      <c r="E6" s="4">
-        <v>90279149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C45" s="2">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <f t="shared" ca="1" si="0"/>
+        <v>652504</v>
+      </c>
+      <c r="F45">
+        <v>725004</v>
+      </c>
+      <c r="G45" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4">
-        <v>180177056</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4">
-        <v>13305452</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4">
-        <v>8948035</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <f t="shared" ca="1" si="0"/>
+        <v>62161440</v>
+      </c>
+      <c r="F48">
+        <v>56510400</v>
+      </c>
+      <c r="G48" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s">
+        <v>36</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4">
-        <v>140931564</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4">
-        <v>17896071</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="2">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4">
-        <v>31318125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4">
-        <v>53688215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4">
-        <v>43365104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4">
-        <v>40213942</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="C50" s="2">
+        <v>1</v>
+      </c>
+      <c r="D50" s="2">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <f t="shared" ca="1" si="0"/>
+        <v>148533333</v>
+      </c>
+      <c r="F50">
+        <v>148533333</v>
+      </c>
+      <c r="G50" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="2">
-        <v>1</v>
-      </c>
-      <c r="D16" s="2">
-        <v>1</v>
-      </c>
-      <c r="E16" s="4">
-        <v>219201481</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1</v>
-      </c>
-      <c r="D17" s="2">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4">
-        <v>61220888</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="2">
-        <v>1</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4">
-        <v>84680592</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2">
-        <v>5</v>
-      </c>
-      <c r="E19" s="4">
-        <v>3625021</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="2">
-        <v>1</v>
-      </c>
-      <c r="D20" s="2">
-        <v>5</v>
-      </c>
-      <c r="E20" s="4">
-        <v>13464366</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="2">
-        <v>1</v>
-      </c>
-      <c r="D21" s="2">
-        <v>5</v>
-      </c>
-      <c r="E21" s="4">
-        <v>5390769</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="2">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4">
-        <v>56510400</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="2">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2">
-        <v>1</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="2">
-        <v>1</v>
-      </c>
-      <c r="D24" s="2">
-        <v>1</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="C51" s="2">
+        <v>1</v>
+      </c>
+      <c r="D51" s="2">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <f t="shared" ca="1" si="0"/>
+        <v>148530434</v>
+      </c>
+      <c r="F51">
+        <v>185663042</v>
+      </c>
+      <c r="G51" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="2">
-        <v>1</v>
-      </c>
-      <c r="D25" s="2">
-        <v>3</v>
-      </c>
-      <c r="E25" s="4">
-        <v>185663042</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="B52" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="2">
-        <v>1</v>
-      </c>
-      <c r="D26" s="2">
-        <v>3</v>
-      </c>
-      <c r="E26" s="4">
-        <v>20000000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="2">
-        <v>1</v>
-      </c>
-      <c r="D27" s="2">
-        <v>3</v>
-      </c>
-      <c r="E27" s="4">
-        <v>148533333</v>
+      <c r="C52" s="2">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <f t="shared" ca="1" si="0"/>
+        <v>3600000</v>
+      </c>
+      <c r="F52">
+        <v>4000000</v>
+      </c>
+      <c r="G52" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P53" xr:uid="{86710C76-81AC-48E5-8A5F-29B3CE6BD5DC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFBA2FAA-95C5-423D-A8C0-3A912D67D407}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1158,36 +2179,225 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2">
+        <f>ROUND(C2,0)</f>
+        <v>3694296</v>
+      </c>
+      <c r="C2">
+        <f>Medium_Capacity!C49*0.25</f>
+        <v>3694295.5570033002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B18" si="0">ROUND(C3,0)</f>
+        <v>82819787</v>
+      </c>
+      <c r="C3">
+        <f>Medium_Capacity!C50*0.25</f>
+        <v>82819787.354738995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>6513039</v>
+      </c>
+      <c r="C4">
+        <f>Medium_Capacity!C51*0.25</f>
+        <v>6513038.9940517964</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>1795008</v>
+      </c>
+      <c r="C5">
+        <f>Medium_Capacity!C52*0.25</f>
+        <v>1795007.6874129353</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>60870627</v>
+      </c>
+      <c r="C6">
+        <f>Medium_Capacity!C53*0.25</f>
+        <v>60870627.147684671</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>1601225</v>
+      </c>
+      <c r="C7">
+        <f>Medium_Capacity!C54*0.25</f>
+        <v>1601225.4899671054</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>15513538</v>
+      </c>
+      <c r="C8">
+        <f>Medium_Capacity!C55*0.25</f>
+        <v>15513537.879683325</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>1456644</v>
+      </c>
+      <c r="C9">
+        <f>Medium_Capacity!C56*0.25</f>
+        <v>1456644.232631579</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>29</v>
       </c>
-      <c r="B2">
-        <v>12542</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>63195503</v>
+      </c>
+      <c r="C10">
+        <f>Medium_Capacity!C57*0.25</f>
+        <v>63195503.325986847</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <f>Medium_Capacity!C58*0.25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>20944762</v>
+      </c>
+      <c r="C12">
+        <f>Medium_Capacity!C59*0.25</f>
+        <v>20944761.71187168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>34</v>
       </c>
-      <c r="B3">
-        <v>7598</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4">
-        <v>14598</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>109600741</v>
+      </c>
+      <c r="C13">
+        <f>Medium_Capacity!C60*0.25</f>
+        <v>109600740.51114175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>4747052</v>
+      </c>
+      <c r="C14">
+        <f>Medium_Capacity!C61*0.25</f>
+        <v>4747052.4303343054</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>14875638</v>
+      </c>
+      <c r="C15">
+        <f>Medium_Capacity!C62*0.25</f>
+        <v>14875638.036021562</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>231909</v>
+      </c>
+      <c r="C16">
+        <f>Medium_Capacity!C63*0.25</f>
+        <v>231909.45848684199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>35619751</v>
+      </c>
+      <c r="C17">
+        <f>Medium_Capacity!C64*0.25</f>
+        <v>35619750.841946572</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>13</v>
       </c>
-      <c r="B5">
-        <v>5145</v>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>40200058</v>
+      </c>
+      <c r="C18">
+        <f>Medium_Capacity!C65*0.25</f>
+        <v>40200058.257479519</v>
       </c>
     </row>
   </sheetData>
@@ -1197,118 +2407,2563 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C2B8D5-A351-43B6-AB72-03AAE787B34B}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="21">
+        <f>C2</f>
         <v>37210000</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" s="19">
+        <v>37210000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="21">
+        <f t="shared" ref="B3:B13" si="0">C3</f>
         <v>2610000</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" s="19">
+        <v>2610000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="21">
+        <f t="shared" si="0"/>
         <v>35730000</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" s="19">
+        <v>35730000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="21">
+        <f t="shared" si="0"/>
         <v>5706000</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" s="19">
+        <v>5706000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="21">
+        <f t="shared" si="0"/>
         <v>5777000</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" s="19">
+        <v>5777000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="21">
+        <f t="shared" si="0"/>
         <v>3207000</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" s="19">
+        <v>3207000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="21">
+        <f t="shared" si="0"/>
         <v>2595000</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8" s="19">
+        <v>2595000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="21">
+        <f t="shared" si="0"/>
         <v>3123000</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9" s="19">
+        <v>3123000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="21">
+        <f t="shared" si="0"/>
         <v>5222000</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C10" s="19">
+        <v>5222000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="21">
+        <f t="shared" si="0"/>
         <v>1900000</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11" s="19">
+        <v>1900000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="21">
+        <f t="shared" si="0"/>
         <v>14250000</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C12" s="19">
+        <v>14250000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="21">
+        <f t="shared" si="0"/>
+        <v>1608000</v>
+      </c>
+      <c r="C13" s="19">
         <v>1608000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF49103-869D-47A8-B34E-4DAF7BA26C71}">
+  <dimension ref="A1:AZ65"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" customWidth="1"/>
+    <col min="7" max="9" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="12">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
+      <c r="AE1" s="2"/>
+      <c r="AF1" s="2"/>
+      <c r="AG1" s="2"/>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2"/>
+      <c r="AL1" s="2"/>
+      <c r="AM1" s="2"/>
+      <c r="AN1" s="2"/>
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="2"/>
+      <c r="AQ1" s="2"/>
+      <c r="AR1" s="2"/>
+      <c r="AS1" s="2"/>
+      <c r="AT1" s="2"/>
+      <c r="AU1" s="2"/>
+      <c r="AV1" s="2"/>
+      <c r="AW1" s="2"/>
+      <c r="AX1" s="2"/>
+      <c r="AY1" s="2"/>
+      <c r="AZ1" s="2"/>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="8">
+        <v>12600000</v>
+      </c>
+      <c r="C2" s="17">
+        <f>B2/$B$20</f>
+        <v>3.9562237561659988E-3</v>
+      </c>
+      <c r="D2" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A2)</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="15">
+        <f>VLOOKUP(Medium_Capacity!A2, Medium_Capacity!A1:A18:B1:B18, 2, FALSE)</f>
+        <v>12600000</v>
+      </c>
+      <c r="F2" s="20">
+        <f ca="1">E2-D2</f>
+        <v>12600000</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2">
+        <f>VLOOKUP(Q_start!B2,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="K2">
+        <f>VLOOKUP(Q_start!A2,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>14777182.228013201</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="5"/>
+      <c r="AN2" s="5"/>
+      <c r="AO2" s="5"/>
+      <c r="AP2" s="5"/>
+      <c r="AQ2" s="5"/>
+      <c r="AR2" s="5"/>
+      <c r="AS2" s="5"/>
+      <c r="AT2" s="5"/>
+      <c r="AU2" s="5"/>
+      <c r="AV2" s="5"/>
+      <c r="AW2" s="5"/>
+      <c r="AX2" s="5"/>
+      <c r="AY2" s="5"/>
+      <c r="AZ2" s="5"/>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="8">
+        <v>24300000</v>
+      </c>
+      <c r="C3" s="17">
+        <f t="shared" ref="C3:C18" si="0">B3/$B$20</f>
+        <v>7.6298601011772823E-3</v>
+      </c>
+      <c r="D3" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A3)</f>
+        <v>14635997</v>
+      </c>
+      <c r="E3" s="15">
+        <f>VLOOKUP(Medium_Capacity!A3, Medium_Capacity!A2:A19:B2:B19, 2, FALSE)</f>
+        <v>24300000</v>
+      </c>
+      <c r="F3" s="20">
+        <f t="shared" ref="F3:F18" ca="1" si="1">E3-D3</f>
+        <v>9664003</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3">
+        <f>VLOOKUP(Q_start!B3,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>3.6610769045155193E-2</v>
+      </c>
+      <c r="K3">
+        <f>VLOOKUP(Q_start!A3,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>14777182.228013201</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="5"/>
+      <c r="AG3" s="5"/>
+      <c r="AH3" s="5"/>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="5"/>
+      <c r="AM3" s="5"/>
+      <c r="AN3" s="5"/>
+      <c r="AO3" s="5"/>
+      <c r="AP3" s="5"/>
+      <c r="AQ3" s="5"/>
+      <c r="AR3" s="5"/>
+      <c r="AS3" s="5"/>
+      <c r="AT3" s="5"/>
+      <c r="AU3" s="5"/>
+      <c r="AV3" s="5"/>
+      <c r="AW3" s="5"/>
+      <c r="AX3" s="5"/>
+      <c r="AY3" s="5"/>
+      <c r="AZ3" s="5"/>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="8">
+        <v>8000000</v>
+      </c>
+      <c r="C4" s="17">
+        <f t="shared" si="0"/>
+        <v>2.5118880991530147E-3</v>
+      </c>
+      <c r="D4" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A4)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="15">
+        <f>VLOOKUP(Medium_Capacity!A4, Medium_Capacity!A3:A20:B3:B20, 2, FALSE)</f>
+        <v>8000000</v>
+      </c>
+      <c r="F4" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>8000000</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="6"/>
+      <c r="J4">
+        <f>VLOOKUP(Q_start!B4,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="K4">
+        <f>VLOOKUP(Q_start!A4,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>331279149.41895598</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="5"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5"/>
+      <c r="AN4" s="5"/>
+      <c r="AO4" s="5"/>
+      <c r="AP4" s="5"/>
+      <c r="AQ4" s="5"/>
+      <c r="AR4" s="5"/>
+      <c r="AS4" s="5"/>
+      <c r="AT4" s="5"/>
+      <c r="AU4" s="5"/>
+      <c r="AV4" s="5"/>
+      <c r="AW4" s="5"/>
+      <c r="AX4" s="5"/>
+      <c r="AY4" s="5"/>
+      <c r="AZ4" s="5"/>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="8">
+        <v>36000000</v>
+      </c>
+      <c r="C5" s="17">
+        <f>B5/$B$20</f>
+        <v>1.1303496446188567E-2</v>
+      </c>
+      <c r="D5" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A5)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="15">
+        <f>VLOOKUP(Medium_Capacity!A5, Medium_Capacity!A4:A21:B4:B21, 2, FALSE)</f>
+        <v>36000000</v>
+      </c>
+      <c r="F5" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>36000000</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="6"/>
+      <c r="J5">
+        <f>VLOOKUP(Q_start!B5,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>5.0269160584299713E-2</v>
+      </c>
+      <c r="K5">
+        <f>VLOOKUP(Q_start!A5,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>331279149.41895598</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+      <c r="AA5" s="5"/>
+      <c r="AB5" s="5"/>
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="5"/>
+      <c r="AF5" s="5"/>
+      <c r="AG5" s="5"/>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="5"/>
+      <c r="AJ5" s="5"/>
+      <c r="AK5" s="5"/>
+      <c r="AL5" s="5"/>
+      <c r="AM5" s="5"/>
+      <c r="AN5" s="5"/>
+      <c r="AO5" s="5"/>
+      <c r="AP5" s="5"/>
+      <c r="AQ5" s="5"/>
+      <c r="AR5" s="5"/>
+      <c r="AS5" s="5"/>
+      <c r="AT5" s="5"/>
+      <c r="AU5" s="5"/>
+      <c r="AV5" s="5"/>
+      <c r="AW5" s="5"/>
+      <c r="AX5" s="5"/>
+      <c r="AY5" s="5"/>
+      <c r="AZ5" s="5"/>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="8">
+        <v>8400000</v>
+      </c>
+      <c r="C6" s="17">
+        <f t="shared" si="0"/>
+        <v>2.6374825041106656E-3</v>
+      </c>
+      <c r="D6" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A6)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="15">
+        <f>VLOOKUP(Medium_Capacity!A6, Medium_Capacity!A5:A22:B5:B22, 2, FALSE)</f>
+        <v>8400000</v>
+      </c>
+      <c r="F6" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>8400000</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6">
+        <f>VLOOKUP(Q_start!B6,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="K6">
+        <f>VLOOKUP(Q_start!A6,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>26052155.976207186</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="5"/>
+      <c r="AF6" s="5"/>
+      <c r="AG6" s="5"/>
+      <c r="AH6" s="5"/>
+      <c r="AI6" s="5"/>
+      <c r="AJ6" s="5"/>
+      <c r="AK6" s="5"/>
+      <c r="AL6" s="5"/>
+      <c r="AM6" s="5"/>
+      <c r="AN6" s="5"/>
+      <c r="AO6" s="5"/>
+      <c r="AP6" s="5"/>
+      <c r="AQ6" s="5"/>
+      <c r="AR6" s="5"/>
+      <c r="AS6" s="5"/>
+      <c r="AT6" s="5"/>
+      <c r="AU6" s="5"/>
+      <c r="AV6" s="5"/>
+      <c r="AW6" s="5"/>
+      <c r="AX6" s="5"/>
+      <c r="AY6" s="5"/>
+      <c r="AZ6" s="5"/>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="8">
+        <v>160100000</v>
+      </c>
+      <c r="C7" s="17">
+        <f t="shared" si="0"/>
+        <v>5.0269160584299713E-2</v>
+      </c>
+      <c r="D7" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A7)</f>
+        <v>124201806</v>
+      </c>
+      <c r="E7" s="15">
+        <f>VLOOKUP(Medium_Capacity!A7, Medium_Capacity!A6:A23:B6:B23, 2, FALSE)</f>
+        <v>160100000</v>
+      </c>
+      <c r="F7" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>35898194</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7">
+        <f>VLOOKUP(Q_start!B7,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.51693087150507078</v>
+      </c>
+      <c r="K7">
+        <f>VLOOKUP(Q_start!A7,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>26052155.976207186</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
+      <c r="AA7" s="5"/>
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="5"/>
+      <c r="AE7" s="5"/>
+      <c r="AF7" s="5"/>
+      <c r="AG7" s="5"/>
+      <c r="AH7" s="5"/>
+      <c r="AI7" s="5"/>
+      <c r="AJ7" s="5"/>
+      <c r="AK7" s="5"/>
+      <c r="AL7" s="5"/>
+      <c r="AM7" s="5"/>
+      <c r="AN7" s="5"/>
+      <c r="AO7" s="5"/>
+      <c r="AP7" s="5"/>
+      <c r="AQ7" s="5"/>
+      <c r="AR7" s="5"/>
+      <c r="AS7" s="5"/>
+      <c r="AT7" s="5"/>
+      <c r="AU7" s="5"/>
+      <c r="AV7" s="5"/>
+      <c r="AW7" s="5"/>
+      <c r="AX7" s="5"/>
+      <c r="AY7" s="5"/>
+      <c r="AZ7" s="5"/>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="8">
+        <v>30000</v>
+      </c>
+      <c r="C8" s="17">
+        <f t="shared" si="0"/>
+        <v>9.4195803718238052E-6</v>
+      </c>
+      <c r="D8" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A8)</f>
+        <v>30000</v>
+      </c>
+      <c r="E8" s="15">
+        <f>VLOOKUP(Medium_Capacity!A8, Medium_Capacity!A7:A24:B7:B24, 2, FALSE)</f>
+        <v>30000</v>
+      </c>
+      <c r="F8" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8">
+        <f>VLOOKUP(Q_start!B8,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>9.7335663842179328E-4</v>
+      </c>
+      <c r="K8">
+        <f>VLOOKUP(Q_start!A8,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>26052155.976207186</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="5"/>
+      <c r="AB8" s="5"/>
+      <c r="AC8" s="5"/>
+      <c r="AD8" s="5"/>
+      <c r="AE8" s="5"/>
+      <c r="AF8" s="5"/>
+      <c r="AG8" s="5"/>
+      <c r="AH8" s="5"/>
+      <c r="AI8" s="5"/>
+      <c r="AJ8" s="5"/>
+      <c r="AK8" s="5"/>
+      <c r="AL8" s="5"/>
+      <c r="AM8" s="5"/>
+      <c r="AN8" s="5"/>
+      <c r="AO8" s="5"/>
+      <c r="AP8" s="5"/>
+      <c r="AQ8" s="5"/>
+      <c r="AR8" s="5"/>
+      <c r="AS8" s="5"/>
+      <c r="AT8" s="5"/>
+      <c r="AU8" s="5"/>
+      <c r="AV8" s="5"/>
+      <c r="AW8" s="5"/>
+      <c r="AX8" s="5"/>
+      <c r="AY8" s="5"/>
+      <c r="AZ8" s="5"/>
+    </row>
+    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1646350000</v>
+      </c>
+      <c r="C9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.51693087150507078</v>
+      </c>
+      <c r="D9" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A9)</f>
+        <v>501049488</v>
+      </c>
+      <c r="E9" s="15">
+        <f>VLOOKUP(Medium_Capacity!A9, Medium_Capacity!A8:A25:B8:B25, 2, FALSE)</f>
+        <v>1646350000</v>
+      </c>
+      <c r="F9" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>1145300512</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9">
+        <f>VLOOKUP(Q_start!B9,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="K9">
+        <f>VLOOKUP(Q_start!A9,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>7180030.7496517412</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5"/>
+      <c r="AB9" s="5"/>
+      <c r="AC9" s="5"/>
+      <c r="AD9" s="5"/>
+      <c r="AE9" s="5"/>
+      <c r="AF9" s="5"/>
+      <c r="AG9" s="5"/>
+      <c r="AH9" s="5"/>
+      <c r="AI9" s="5"/>
+      <c r="AJ9" s="5"/>
+      <c r="AK9" s="5"/>
+      <c r="AL9" s="5"/>
+      <c r="AM9" s="5"/>
+      <c r="AN9" s="5"/>
+      <c r="AO9" s="5"/>
+      <c r="AP9" s="5"/>
+      <c r="AQ9" s="5"/>
+      <c r="AR9" s="5"/>
+      <c r="AS9" s="5"/>
+      <c r="AT9" s="5"/>
+      <c r="AU9" s="5"/>
+      <c r="AV9" s="5"/>
+      <c r="AW9" s="5"/>
+      <c r="AX9" s="5"/>
+      <c r="AY9" s="5"/>
+      <c r="AZ9" s="5"/>
+    </row>
+    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="8">
+        <v>8000000</v>
+      </c>
+      <c r="C10" s="17">
+        <f t="shared" si="0"/>
+        <v>2.5118880991530147E-3</v>
+      </c>
+      <c r="D10" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A10)</f>
+        <v>5400000</v>
+      </c>
+      <c r="E10" s="15">
+        <f>VLOOKUP(Medium_Capacity!A10, Medium_Capacity!A9:A26:B9:B26, 2, FALSE)</f>
+        <v>8000000</v>
+      </c>
+      <c r="F10" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>2600000</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10">
+        <f>VLOOKUP(Q_start!B10,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>3.6610769045155193E-2</v>
+      </c>
+      <c r="K10">
+        <f>VLOOKUP(Q_start!A10,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>7180030.7496517412</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="5"/>
+      <c r="AF10" s="5"/>
+      <c r="AG10" s="5"/>
+      <c r="AH10" s="5"/>
+      <c r="AI10" s="5"/>
+      <c r="AJ10" s="5"/>
+      <c r="AK10" s="5"/>
+      <c r="AL10" s="5"/>
+      <c r="AM10" s="5"/>
+      <c r="AN10" s="5"/>
+      <c r="AO10" s="5"/>
+      <c r="AP10" s="5"/>
+      <c r="AQ10" s="5"/>
+      <c r="AR10" s="5"/>
+      <c r="AS10" s="5"/>
+      <c r="AT10" s="5"/>
+      <c r="AU10" s="5"/>
+      <c r="AV10" s="5"/>
+      <c r="AW10" s="5"/>
+      <c r="AX10" s="5"/>
+      <c r="AY10" s="5"/>
+      <c r="AZ10" s="5"/>
+    </row>
+    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="8">
+        <v>60600000</v>
+      </c>
+      <c r="C11" s="17">
+        <f t="shared" si="0"/>
+        <v>1.9027552351084089E-2</v>
+      </c>
+      <c r="D11" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A11)</f>
+        <v>66152801</v>
+      </c>
+      <c r="E11" s="15">
+        <f>VLOOKUP(Medium_Capacity!A11, Medium_Capacity!A10:A27:B10:B27, 2, FALSE)</f>
+        <v>60600000</v>
+      </c>
+      <c r="F11" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>-5552801</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11">
+        <f>VLOOKUP(Q_start!B11,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>7.6298601011772823E-3</v>
+      </c>
+      <c r="K11">
+        <f>VLOOKUP(Q_start!A11,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>7180030.7496517412</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+      <c r="AA11" s="5"/>
+      <c r="AB11" s="5"/>
+      <c r="AC11" s="5"/>
+      <c r="AD11" s="5"/>
+      <c r="AE11" s="5"/>
+      <c r="AF11" s="5"/>
+      <c r="AG11" s="5"/>
+      <c r="AH11" s="5"/>
+      <c r="AI11" s="5"/>
+      <c r="AJ11" s="5"/>
+      <c r="AK11" s="5"/>
+      <c r="AL11" s="5"/>
+      <c r="AM11" s="5"/>
+      <c r="AN11" s="5"/>
+      <c r="AO11" s="5"/>
+      <c r="AP11" s="5"/>
+      <c r="AQ11" s="5"/>
+      <c r="AR11" s="5"/>
+      <c r="AS11" s="5"/>
+      <c r="AT11" s="5"/>
+      <c r="AU11" s="5"/>
+      <c r="AV11" s="5"/>
+      <c r="AW11" s="5"/>
+      <c r="AX11" s="5"/>
+      <c r="AY11" s="5"/>
+      <c r="AZ11" s="5"/>
+    </row>
+    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="8">
+        <v>3100000</v>
+      </c>
+      <c r="C12" s="17">
+        <f t="shared" si="0"/>
+        <v>9.7335663842179328E-4</v>
+      </c>
+      <c r="D12" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A12)</f>
+        <v>3053115</v>
+      </c>
+      <c r="E12" s="15">
+        <f>VLOOKUP(Medium_Capacity!A12, Medium_Capacity!A11:A28:B11:B28, 2, FALSE)</f>
+        <v>3100000</v>
+      </c>
+      <c r="F12" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>46885</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12">
+        <f>VLOOKUP(Q_start!B12,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="K12">
+        <f>VLOOKUP(Q_start!A12,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>59502552.144086249</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
+      <c r="AA12" s="5"/>
+      <c r="AB12" s="5"/>
+      <c r="AC12" s="5"/>
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="5"/>
+      <c r="AF12" s="5"/>
+      <c r="AG12" s="5"/>
+      <c r="AH12" s="5"/>
+      <c r="AI12" s="5"/>
+      <c r="AJ12" s="5"/>
+      <c r="AK12" s="5"/>
+      <c r="AL12" s="5"/>
+      <c r="AM12" s="5"/>
+      <c r="AN12" s="5"/>
+      <c r="AO12" s="5"/>
+      <c r="AP12" s="5"/>
+      <c r="AQ12" s="5"/>
+      <c r="AR12" s="5"/>
+      <c r="AS12" s="5"/>
+      <c r="AT12" s="5"/>
+      <c r="AU12" s="5"/>
+      <c r="AV12" s="5"/>
+      <c r="AW12" s="5"/>
+      <c r="AX12" s="5"/>
+      <c r="AY12" s="5"/>
+      <c r="AZ12" s="5"/>
+    </row>
+    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="8">
+        <v>20500000</v>
+      </c>
+      <c r="C13" s="17">
+        <f t="shared" si="0"/>
+        <v>6.4367132540796004E-3</v>
+      </c>
+      <c r="D13" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A13)</f>
+        <v>8948035</v>
+      </c>
+      <c r="E13" s="15">
+        <f>VLOOKUP(Medium_Capacity!A13, Medium_Capacity!A12:A29:B12:B29, 2, FALSE)</f>
+        <v>20500000</v>
+      </c>
+      <c r="F13" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>11551965</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13">
+        <f>VLOOKUP(Q_start!B13,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>1.9027552351084089E-2</v>
+      </c>
+      <c r="K13">
+        <f>VLOOKUP(Q_start!A13,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>59502552.144086249</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+      <c r="AA13" s="5"/>
+      <c r="AB13" s="5"/>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="5"/>
+      <c r="AF13" s="5"/>
+      <c r="AG13" s="5"/>
+      <c r="AH13" s="5"/>
+      <c r="AI13" s="5"/>
+      <c r="AJ13" s="5"/>
+      <c r="AK13" s="5"/>
+      <c r="AL13" s="5"/>
+      <c r="AM13" s="5"/>
+      <c r="AN13" s="5"/>
+      <c r="AO13" s="5"/>
+      <c r="AP13" s="5"/>
+      <c r="AQ13" s="5"/>
+      <c r="AR13" s="5"/>
+      <c r="AS13" s="5"/>
+      <c r="AT13" s="5"/>
+      <c r="AU13" s="5"/>
+      <c r="AV13" s="5"/>
+      <c r="AW13" s="5"/>
+      <c r="AX13" s="5"/>
+      <c r="AY13" s="5"/>
+      <c r="AZ13" s="5"/>
+    </row>
+    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="8">
+        <v>5800000</v>
+      </c>
+      <c r="C14" s="17">
+        <f t="shared" si="0"/>
+        <v>1.8211188718859359E-3</v>
+      </c>
+      <c r="D14" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A14)</f>
+        <v>3600000</v>
+      </c>
+      <c r="E14" s="15">
+        <f>VLOOKUP(Medium_Capacity!A14, Medium_Capacity!A13:A30:B13:B30, 2, FALSE)</f>
+        <v>5800000</v>
+      </c>
+      <c r="F14" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>2200000</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14">
+        <f>VLOOKUP(Q_start!B14,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="K14">
+        <f>VLOOKUP(Q_start!A14,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>927637.83394736797</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+      <c r="AA14" s="5"/>
+      <c r="AB14" s="5"/>
+      <c r="AC14" s="5"/>
+      <c r="AD14" s="5"/>
+      <c r="AE14" s="5"/>
+      <c r="AF14" s="5"/>
+      <c r="AG14" s="5"/>
+      <c r="AH14" s="5"/>
+      <c r="AI14" s="5"/>
+      <c r="AJ14" s="5"/>
+      <c r="AK14" s="5"/>
+      <c r="AL14" s="5"/>
+      <c r="AM14" s="5"/>
+      <c r="AN14" s="5"/>
+      <c r="AO14" s="5"/>
+      <c r="AP14" s="5"/>
+      <c r="AQ14" s="5"/>
+      <c r="AR14" s="5"/>
+      <c r="AS14" s="5"/>
+      <c r="AT14" s="5"/>
+      <c r="AU14" s="5"/>
+      <c r="AV14" s="5"/>
+      <c r="AW14" s="5"/>
+      <c r="AX14" s="5"/>
+      <c r="AY14" s="5"/>
+      <c r="AZ14" s="5"/>
+    </row>
+    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="8">
+        <v>116600000</v>
+      </c>
+      <c r="C15" s="17">
+        <f t="shared" si="0"/>
+        <v>3.6610769045155193E-2</v>
+      </c>
+      <c r="D15" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A15)</f>
+        <v>87588183</v>
+      </c>
+      <c r="E15" s="15">
+        <f>VLOOKUP(Medium_Capacity!A15, Medium_Capacity!A14:A31:B14:B31, 2, FALSE)</f>
+        <v>116600000</v>
+      </c>
+      <c r="F15" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>29011817</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15">
+        <f>VLOOKUP(Q_start!B15,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>3.2842936896425673E-2</v>
+      </c>
+      <c r="K15">
+        <f>VLOOKUP(Q_start!A15,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>927637.83394736797</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="5"/>
+      <c r="AB15" s="5"/>
+      <c r="AC15" s="5"/>
+      <c r="AD15" s="5"/>
+      <c r="AE15" s="5"/>
+      <c r="AF15" s="5"/>
+      <c r="AG15" s="5"/>
+      <c r="AH15" s="5"/>
+      <c r="AI15" s="5"/>
+      <c r="AJ15" s="5"/>
+      <c r="AK15" s="5"/>
+      <c r="AL15" s="5"/>
+      <c r="AM15" s="5"/>
+      <c r="AN15" s="5"/>
+      <c r="AO15" s="5"/>
+      <c r="AP15" s="5"/>
+      <c r="AQ15" s="5"/>
+      <c r="AR15" s="5"/>
+      <c r="AS15" s="5"/>
+      <c r="AT15" s="5"/>
+      <c r="AU15" s="5"/>
+      <c r="AV15" s="5"/>
+      <c r="AW15" s="5"/>
+      <c r="AX15" s="5"/>
+      <c r="AY15" s="5"/>
+      <c r="AZ15" s="5"/>
+    </row>
+    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="8">
+        <v>104600000</v>
+      </c>
+      <c r="C16" s="17">
+        <f t="shared" si="0"/>
+        <v>3.2842936896425673E-2</v>
+      </c>
+      <c r="D16" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A16)</f>
+        <v>125503191</v>
+      </c>
+      <c r="E16" s="15">
+        <f>VLOOKUP(Medium_Capacity!A16, Medium_Capacity!A15:A32:B15:B32, 2, FALSE)</f>
+        <v>104600000</v>
+      </c>
+      <c r="F16" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>-20903191</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16">
+        <f>VLOOKUP(Q_start!B16,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>9.4195803718238052E-6</v>
+      </c>
+      <c r="K16">
+        <f>VLOOKUP(Q_start!A16,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>927637.83394736797</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
+      <c r="AA16" s="5"/>
+      <c r="AB16" s="5"/>
+      <c r="AC16" s="5"/>
+      <c r="AD16" s="5"/>
+      <c r="AE16" s="5"/>
+      <c r="AF16" s="5"/>
+      <c r="AG16" s="5"/>
+      <c r="AH16" s="5"/>
+      <c r="AI16" s="5"/>
+      <c r="AJ16" s="5"/>
+      <c r="AK16" s="5"/>
+      <c r="AL16" s="5"/>
+      <c r="AM16" s="5"/>
+      <c r="AN16" s="5"/>
+      <c r="AO16" s="5"/>
+      <c r="AP16" s="5"/>
+      <c r="AQ16" s="5"/>
+      <c r="AR16" s="5"/>
+      <c r="AS16" s="5"/>
+      <c r="AT16" s="5"/>
+      <c r="AU16" s="5"/>
+      <c r="AV16" s="5"/>
+      <c r="AW16" s="5"/>
+      <c r="AX16" s="5"/>
+      <c r="AY16" s="5"/>
+      <c r="AZ16" s="5"/>
+    </row>
+    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="8">
+        <v>969375250</v>
+      </c>
+      <c r="C17" s="17">
+        <f t="shared" si="0"/>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="D17" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A17)</f>
+        <v>494157473</v>
+      </c>
+      <c r="E17" s="15">
+        <f>VLOOKUP(Medium_Capacity!A17, Medium_Capacity!A16:A33:B16:B33, 2, FALSE)</f>
+        <v>969375250</v>
+      </c>
+      <c r="F17" s="20">
+        <f ca="1">E17-D17</f>
+        <v>475217777</v>
+      </c>
+      <c r="J17">
+        <f>VLOOKUP(Q_start!B17,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>1.9027552351084089E-2</v>
+      </c>
+      <c r="K17">
+        <f>VLOOKUP(Q_start!A17,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>83779046.847486719</v>
+      </c>
+      <c r="L17" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5"/>
+      <c r="Z17" s="5"/>
+      <c r="AA17" s="5"/>
+      <c r="AB17" s="5"/>
+      <c r="AC17" s="5"/>
+      <c r="AD17" s="5"/>
+      <c r="AE17" s="5"/>
+      <c r="AF17" s="5"/>
+      <c r="AG17" s="5"/>
+      <c r="AH17" s="5"/>
+      <c r="AI17" s="5"/>
+      <c r="AJ17" s="5"/>
+      <c r="AK17" s="5"/>
+      <c r="AL17" s="5"/>
+      <c r="AM17" s="5"/>
+      <c r="AN17" s="5"/>
+      <c r="AO17" s="5"/>
+      <c r="AP17" s="5"/>
+      <c r="AQ17" s="5"/>
+      <c r="AR17" s="5"/>
+      <c r="AS17" s="5"/>
+      <c r="AT17" s="5"/>
+      <c r="AU17" s="5"/>
+      <c r="AV17" s="5"/>
+      <c r="AW17" s="5"/>
+      <c r="AX17" s="5"/>
+      <c r="AY17" s="5"/>
+      <c r="AZ17" s="5"/>
+    </row>
+    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="8">
+        <v>500000</v>
+      </c>
+      <c r="C18" s="17">
+        <f t="shared" si="0"/>
+        <v>1.5699300619706342E-4</v>
+      </c>
+      <c r="D18" s="16">
+        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A18)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="15">
+        <f>VLOOKUP(Medium_Capacity!A18, Medium_Capacity!A17:A34:B17:B34, 2, FALSE)</f>
+        <v>500000</v>
+      </c>
+      <c r="F18" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>500000</v>
+      </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18">
+        <f>VLOOKUP(Q_start!B18,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>3.9562237561659988E-3</v>
+      </c>
+      <c r="K18">
+        <f>VLOOKUP(Q_start!A18,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>83779046.847486719</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+      <c r="AA18" s="5"/>
+      <c r="AB18" s="5"/>
+      <c r="AC18" s="5"/>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="5"/>
+      <c r="AG18" s="5"/>
+      <c r="AH18" s="5"/>
+      <c r="AI18" s="5"/>
+      <c r="AJ18" s="5"/>
+      <c r="AK18" s="5"/>
+      <c r="AL18" s="5"/>
+      <c r="AM18" s="5"/>
+      <c r="AN18" s="5"/>
+      <c r="AO18" s="5"/>
+      <c r="AP18" s="5"/>
+      <c r="AQ18" s="5"/>
+      <c r="AR18" s="5"/>
+      <c r="AS18" s="5"/>
+      <c r="AT18" s="5"/>
+      <c r="AU18" s="5"/>
+      <c r="AV18" s="5"/>
+      <c r="AW18" s="5"/>
+      <c r="AX18" s="5"/>
+      <c r="AY18" s="5"/>
+      <c r="AZ18" s="5"/>
+    </row>
+    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19">
+        <f>VLOOKUP(Q_start!B19,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>2.6374825041106656E-3</v>
+      </c>
+      <c r="K19">
+        <f>VLOOKUP(Q_start!A19,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>83779046.847486719</v>
+      </c>
+      <c r="L19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="B20" s="9">
+        <f>SUM(B2:B18)</f>
+        <v>3184855250</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20">
+        <f>VLOOKUP(Q_start!B20,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>3.2842936896425673E-2</v>
+      </c>
+      <c r="K20">
+        <f>VLOOKUP(Q_start!A20,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>83779046.847486719</v>
+      </c>
+      <c r="L20" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21">
+        <f>VLOOKUP(Q_start!B21,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="K21">
+        <f>VLOOKUP(Q_start!A21,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>438402962.04456699</v>
+      </c>
+      <c r="L21" t="s">
+        <v>34</v>
+      </c>
+      <c r="M21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22">
+        <f>VLOOKUP(Q_start!B22,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>3.6610769045155193E-2</v>
+      </c>
+      <c r="K22">
+        <f>VLOOKUP(Q_start!A22,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>438402962.04456699</v>
+      </c>
+      <c r="L22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23">
+        <f>VLOOKUP(Q_start!B23,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.51693087150507078</v>
+      </c>
+      <c r="K23">
+        <f>VLOOKUP(Q_start!A23,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>438402962.04456699</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24">
+        <f>VLOOKUP(Q_start!B24,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>3.2842936896425673E-2</v>
+      </c>
+      <c r="K24">
+        <f>VLOOKUP(Q_start!A24,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>438402962.04456699</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25">
+        <f>VLOOKUP(Q_start!B25,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>6.4367132540796004E-3</v>
+      </c>
+      <c r="K25">
+        <f>VLOOKUP(Q_start!A25,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>438402962.04456699</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26">
+        <f>VLOOKUP(Q_start!B26,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>2.5118880991530147E-3</v>
+      </c>
+      <c r="K26">
+        <f>VLOOKUP(Q_start!A26,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>438402962.04456699</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27">
+        <f>VLOOKUP(Q_start!B27,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>1.1303496446188567E-2</v>
+      </c>
+      <c r="K27">
+        <f>VLOOKUP(Q_start!A27,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>438402962.04456699</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28">
+        <f>VLOOKUP(Q_start!B28,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>2.5118880991530147E-3</v>
+      </c>
+      <c r="K28">
+        <f>VLOOKUP(Q_start!A28,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>438402962.04456699</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29">
+        <f>VLOOKUP(Q_start!B29,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="K29">
+        <f>VLOOKUP(Q_start!A29,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>6404901.9598684218</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="2">
+        <v>3.9562237561659988E-3</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30">
+        <f>VLOOKUP(Q_start!B30,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>3.6610769045155193E-2</v>
+      </c>
+      <c r="K30">
+        <f>VLOOKUP(Q_start!A30,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>6404901.9598684218</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M30" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="2">
+        <v>7.6298601011772823E-3</v>
+      </c>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31">
+        <f>VLOOKUP(Q_start!B31,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>7.6298601011772823E-3</v>
+      </c>
+      <c r="K31">
+        <f>VLOOKUP(Q_start!A31,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>6404901.9598684218</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="2">
+        <v>2.5118880991530147E-3</v>
+      </c>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32">
+        <f>VLOOKUP(Q_start!B32,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="K32">
+        <f>VLOOKUP(Q_start!A32,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>243482508.59073868</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1.1303496446188567E-2</v>
+      </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33">
+        <f>VLOOKUP(Q_start!B33,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>3.6610769045155193E-2</v>
+      </c>
+      <c r="K33">
+        <f>VLOOKUP(Q_start!A33,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>243482508.59073868</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2.6374825041106656E-3</v>
+      </c>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34">
+        <f>VLOOKUP(Q_start!B34,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>7.6298601011772823E-3</v>
+      </c>
+      <c r="K34">
+        <f>VLOOKUP(Q_start!A34,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>243482508.59073868</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M34" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="2">
+        <v>5.0269160584299713E-2</v>
+      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35">
+        <f>VLOOKUP(Q_start!B35,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="K35">
+        <f>VLOOKUP(Q_start!A35,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>62054151.5187333</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M35" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="2">
+        <v>9.4195803718238052E-6</v>
+      </c>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36">
+        <f>VLOOKUP(Q_start!B36,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>5.0269160584299713E-2</v>
+      </c>
+      <c r="K36">
+        <f>VLOOKUP(Q_start!A36,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>62054151.5187333</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M36" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.51693087150507078</v>
+      </c>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37">
+        <f>VLOOKUP(Q_start!B37,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="K37">
+        <f>VLOOKUP(Q_start!A37,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>5826576.9305263162</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M37" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2.5118880991530147E-3</v>
+      </c>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38">
+        <f>VLOOKUP(Q_start!B38,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="K38">
+        <f>VLOOKUP(Q_start!A38,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>252782013.30394739</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M38" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1.9027552351084089E-2</v>
+      </c>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39">
+        <f>VLOOKUP(Q_start!B39,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>3.6610769045155193E-2</v>
+      </c>
+      <c r="K39">
+        <f>VLOOKUP(Q_start!A39,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>252782013.30394739</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M39" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="2">
+        <v>9.7335663842179328E-4</v>
+      </c>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40">
+        <f>VLOOKUP(Q_start!B40,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>5.0269160584299713E-2</v>
+      </c>
+      <c r="K40">
+        <f>VLOOKUP(Q_start!A40,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>252782013.30394739</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M40" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="2">
+        <v>6.4367132540796004E-3</v>
+      </c>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41">
+        <f>VLOOKUP(Q_start!B41,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>1.9027552351084089E-2</v>
+      </c>
+      <c r="K41">
+        <f>VLOOKUP(Q_start!A41,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>252782013.30394739</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M41" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1.8211188718859359E-3</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42">
+        <f>VLOOKUP(Q_start!B42,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>6.4367132540796004E-3</v>
+      </c>
+      <c r="K42">
+        <f>VLOOKUP(Q_start!A42,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>252782013.30394739</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M42" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="2">
+        <v>3.6610769045155193E-2</v>
+      </c>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43">
+        <f>VLOOKUP(Q_start!B43,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>3.2842936896425673E-2</v>
+      </c>
+      <c r="K43">
+        <f>VLOOKUP(Q_start!A43,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M43" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="2">
+        <v>3.2842936896425673E-2</v>
+      </c>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44">
+        <f>VLOOKUP(Q_start!B44,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.51693087150507078</v>
+      </c>
+      <c r="K44">
+        <f>VLOOKUP(Q_start!A44,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>18988209.721337222</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M44" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="J45">
+        <f>VLOOKUP(Q_start!B45,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>9.7335663842179328E-4</v>
+      </c>
+      <c r="K45">
+        <f>VLOOKUP(Q_start!A45,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>18988209.721337222</v>
+      </c>
+      <c r="L45" t="s">
+        <v>9</v>
+      </c>
+      <c r="M45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1.5699300619706342E-4</v>
+      </c>
+      <c r="J46">
+        <f>VLOOKUP(Q_start!B46,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>1.5699300619706342E-4</v>
+      </c>
+      <c r="K46">
+        <f>VLOOKUP(Q_start!A46,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>18988209.721337222</v>
+      </c>
+      <c r="L46" t="s">
+        <v>9</v>
+      </c>
+      <c r="M46" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="J47">
+        <f>VLOOKUP(Q_start!B47,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="K47">
+        <f>VLOOKUP(Q_start!A47,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>142479003.36778629</v>
+      </c>
+      <c r="L47" t="s">
+        <v>10</v>
+      </c>
+      <c r="M47" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="J48">
+        <f>VLOOKUP(Q_start!B48,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.51693087150507078</v>
+      </c>
+      <c r="K48">
+        <f>VLOOKUP(Q_start!A48,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>142479003.36778629</v>
+      </c>
+      <c r="L48" t="s">
+        <v>10</v>
+      </c>
+      <c r="M48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="2">
+        <v>14777182.228013201</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="J49">
+        <f>VLOOKUP(Q_start!B49,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>1.1303496446188567E-2</v>
+      </c>
+      <c r="K49">
+        <f>VLOOKUP(Q_start!A49,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>142479003.36778629</v>
+      </c>
+      <c r="L49" t="s">
+        <v>10</v>
+      </c>
+      <c r="M49" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="2">
+        <v>331279149.41895598</v>
+      </c>
+      <c r="D50" s="2"/>
+      <c r="J50">
+        <f>VLOOKUP(Q_start!B50,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.30437026926105981</v>
+      </c>
+      <c r="K50">
+        <f>VLOOKUP(Q_start!A50,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>160800233.02991807</v>
+      </c>
+      <c r="L50" t="s">
+        <v>13</v>
+      </c>
+      <c r="M50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="2">
+        <v>26052155.976207186</v>
+      </c>
+      <c r="D51" s="2"/>
+      <c r="J51">
+        <f>VLOOKUP(Q_start!B51,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>0.51693087150507078</v>
+      </c>
+      <c r="K51">
+        <f>VLOOKUP(Q_start!A51,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>160800233.02991807</v>
+      </c>
+      <c r="L51" t="s">
+        <v>13</v>
+      </c>
+      <c r="M51" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" s="2">
+        <v>7180030.7496517412</v>
+      </c>
+      <c r="D52" s="2"/>
+      <c r="J52">
+        <f>VLOOKUP(Q_start!B52,Medium_Capacity!$B$30:$C$46,2)</f>
+        <v>1.8211188718859359E-3</v>
+      </c>
+      <c r="K52">
+        <f>VLOOKUP(Q_start!A52,Medium_Capacity!$B$49:$C$65,2, FALSE)</f>
+        <v>160800233.02991807</v>
+      </c>
+      <c r="L52" t="s">
+        <v>13</v>
+      </c>
+      <c r="M52" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" s="2">
+        <v>243482508.59073868</v>
+      </c>
+      <c r="D53" s="2"/>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>41</v>
+      </c>
+      <c r="C54" s="2">
+        <v>6404901.9598684218</v>
+      </c>
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>42</v>
+      </c>
+      <c r="C55" s="2">
+        <v>62054151.5187333</v>
+      </c>
+      <c r="D55" s="2"/>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>43</v>
+      </c>
+      <c r="C56">
+        <v>5826576.9305263162</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57">
+        <v>252782013.30394739</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>44</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59">
+        <v>83779046.847486719</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>34</v>
+      </c>
+      <c r="C60">
+        <v>438402962.04456699</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61">
+        <v>18988209.721337222</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>40</v>
+      </c>
+      <c r="C62">
+        <v>59502552.144086249</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63">
+        <v>927637.83394736797</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64">
+        <v>142479003.36778629</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65">
+        <v>160800233.02991807</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Starting_point.xlsx
+++ b/Starting_point.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/horizon excursion/15 years - Initial Condition sensitivity/starts/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="872" documentId="13_ncr:1_{30A8FEE2-BE8F-4FE6-A73D-C8D61511F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32972361-2A4C-49FE-B2B6-9A3224C8A879}"/>
+  <xr:revisionPtr revIDLastSave="963" documentId="13_ncr:1_{30A8FEE2-BE8F-4FE6-A73D-C8D61511F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF66EB9F-3A1B-4FC0-882C-92AC0AAADD8E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="61">
   <si>
     <t>Measles</t>
   </si>
@@ -217,6 +217,18 @@
   </si>
   <si>
     <t>antigen demand</t>
+  </si>
+  <si>
+    <t>.025 demand</t>
+  </si>
+  <si>
+    <t>Rand</t>
+  </si>
+  <si>
+    <t>ran val</t>
+  </si>
+  <si>
+    <t>rand</t>
   </si>
 </sst>
 </file>
@@ -375,10 +387,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -666,7 +674,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -677,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -688,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -699,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -710,7 +718,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -721,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -732,7 +740,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -743,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -754,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -765,7 +773,7 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -776,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -787,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -840,18 +848,17 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <f ca="1">ROUND(F2*G2,0)</f>
+        <f>ROUND(F2*G2,0)</f>
         <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2" s="22">
-        <f ca="1">RANDBETWEEN(8,12)/10</f>
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -865,18 +872,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E52" ca="1" si="0">ROUND(F3*G3,0)</f>
-        <v>15959357</v>
+        <f>ROUND(F3*G3,0)</f>
+        <v>13299464</v>
       </c>
       <c r="F3">
         <v>13299464</v>
       </c>
       <c r="G3" s="22">
-        <f t="shared" ref="G3:G52" ca="1" si="1">RANDBETWEEN(8,12)/10</f>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -890,18 +896,17 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ref="E4:E52" si="0">ROUND(F4*G4,0)</f>
         <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -918,18 +923,17 @@
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <f t="shared" ca="1" si="0"/>
-        <v>81251234</v>
+        <v>2</v>
+      </c>
+      <c r="E5" s="7">
+        <f>ROUND(F5*G5,0)</f>
+        <v>90279149</v>
       </c>
       <c r="F5">
         <v>90279149</v>
       </c>
       <c r="G5" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -946,18 +950,17 @@
         <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <f t="shared" ca="1" si="0"/>
-        <v>16256545</v>
+        <f t="shared" si="0"/>
+        <v>13547121</v>
       </c>
       <c r="F6">
         <v>13547121</v>
       </c>
       <c r="G6" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -974,17 +977,16 @@
         <v>1</v>
       </c>
       <c r="D7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>12505034</v>
       </c>
       <c r="F7">
         <v>12505034</v>
       </c>
       <c r="G7" s="22">
-        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="J7" s="2"/>
@@ -1002,18 +1004,17 @@
         <v>1</v>
       </c>
       <c r="D8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <f t="shared" ca="1" si="0"/>
-        <v>2400611</v>
+        <f t="shared" si="0"/>
+        <v>2182374</v>
       </c>
       <c r="F8">
         <v>2182374</v>
       </c>
       <c r="G8" s="22">
-        <f ca="1">RANDBETWEEN(8,12)/10</f>
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1030,17 +1031,16 @@
         <v>1</v>
       </c>
       <c r="D9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>4334425</v>
       </c>
       <c r="F9" s="23">
         <v>4334425</v>
       </c>
       <c r="G9" s="22">
-        <f ca="1">RANDBETWEEN(8,12)/10</f>
         <v>1</v>
       </c>
       <c r="J9" s="2"/>
@@ -1058,18 +1058,17 @@
         <v>1</v>
       </c>
       <c r="D10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10" s="22">
-        <f ca="1">RANDBETWEEN(8,12)/10</f>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -1086,18 +1085,17 @@
         <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1111,18 +1109,17 @@
         <v>1</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1136,18 +1133,17 @@
         <v>1</v>
       </c>
       <c r="D13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1161,17 +1157,16 @@
         <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14" s="22">
-        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1186,17 +1181,16 @@
         <v>1</v>
       </c>
       <c r="D15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15" s="22">
-        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1211,17 +1205,16 @@
         <v>1</v>
       </c>
       <c r="D16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <f t="shared" ca="1" si="0"/>
-        <v>30000</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="F16" s="23">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="G16" s="22">
-        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="J16" s="2"/>
@@ -1239,18 +1232,17 @@
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17">
-        <f t="shared" ca="1" si="0"/>
-        <v>48256730</v>
+        <f t="shared" si="0"/>
+        <v>40213942</v>
       </c>
       <c r="F17">
         <v>40213942</v>
       </c>
       <c r="G17" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2"/>
     </row>
@@ -1265,18 +1257,17 @@
         <v>1</v>
       </c>
       <c r="D18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J18" s="2"/>
     </row>
@@ -1291,18 +1282,17 @@
         <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2"/>
     </row>
@@ -1317,18 +1307,17 @@
         <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <f t="shared" ca="1" si="0"/>
-        <v>52038125</v>
+        <f t="shared" si="0"/>
+        <v>43365104</v>
       </c>
       <c r="F20">
         <v>43365104</v>
       </c>
       <c r="G20" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2"/>
     </row>
@@ -1343,17 +1332,16 @@
         <v>1</v>
       </c>
       <c r="D21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21" s="22">
-        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1368,18 +1356,17 @@
         <v>1</v>
       </c>
       <c r="D22" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22">
-        <f t="shared" ca="1" si="0"/>
-        <v>46574326</v>
+        <f t="shared" si="0"/>
+        <v>42340296</v>
       </c>
       <c r="F22">
         <v>42340296</v>
       </c>
       <c r="G22" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="O22" s="10"/>
     </row>
@@ -1394,18 +1381,17 @@
         <v>1</v>
       </c>
       <c r="D23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <f t="shared" ca="1" si="0"/>
-        <v>263041777</v>
+        <f t="shared" si="0"/>
+        <v>219201481</v>
       </c>
       <c r="F23">
         <v>219201481</v>
       </c>
       <c r="G23" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="O23" s="10"/>
     </row>
@@ -1420,18 +1406,17 @@
         <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <f t="shared" ca="1" si="0"/>
-        <v>73465066</v>
+        <f t="shared" si="0"/>
+        <v>61220888</v>
       </c>
       <c r="F24">
         <v>61220888</v>
       </c>
       <c r="G24" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J24" s="2"/>
       <c r="O24" s="10"/>
@@ -1447,18 +1432,17 @@
         <v>1</v>
       </c>
       <c r="D25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J25" s="2"/>
       <c r="O25" s="10"/>
@@ -1474,18 +1458,17 @@
         <v>1</v>
       </c>
       <c r="D26" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -1502,17 +1485,16 @@
         <v>1</v>
       </c>
       <c r="D27" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27" s="22">
-        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="I27" s="2"/>
@@ -1530,18 +1512,17 @@
         <v>1</v>
       </c>
       <c r="D28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <f t="shared" ca="1" si="0"/>
-        <v>5400000</v>
+        <f t="shared" si="0"/>
+        <v>6000000</v>
       </c>
       <c r="F28" s="23">
         <v>6000000</v>
       </c>
       <c r="G28" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
@@ -1558,18 +1539,17 @@
         <v>1</v>
       </c>
       <c r="D29" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J29" s="2"/>
       <c r="O29" s="10"/>
@@ -1585,18 +1565,17 @@
         <v>1</v>
       </c>
       <c r="D30" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -1610,18 +1589,17 @@
         <v>1</v>
       </c>
       <c r="D31" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="O31" s="18"/>
       <c r="P31" t="s">
@@ -1639,18 +1617,17 @@
         <v>1</v>
       </c>
       <c r="D32" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32">
-        <f t="shared" ca="1" si="0"/>
-        <v>198194762</v>
+        <f t="shared" si="0"/>
+        <v>180177056</v>
       </c>
       <c r="F32">
         <v>180177056</v>
       </c>
       <c r="G32" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1664,18 +1641,17 @@
         <v>1</v>
       </c>
       <c r="D33" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1689,18 +1665,17 @@
         <v>1</v>
       </c>
       <c r="D34" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <f t="shared" ca="1" si="0"/>
-        <v>14635997</v>
+        <f t="shared" si="0"/>
+        <v>13305452</v>
       </c>
       <c r="F34">
         <v>13305452</v>
       </c>
       <c r="G34" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1714,18 +1689,17 @@
         <v>1</v>
       </c>
       <c r="D35" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
       <c r="G35" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J35" s="2"/>
     </row>
@@ -1740,18 +1714,17 @@
         <v>1</v>
       </c>
       <c r="D36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F36">
         <v>0</v>
       </c>
       <c r="G36" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J36" s="2"/>
     </row>
@@ -1766,18 +1739,17 @@
         <v>1</v>
       </c>
       <c r="D37" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F37">
         <v>0</v>
       </c>
       <c r="G37" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2"/>
     </row>
@@ -1792,18 +1764,17 @@
         <v>1</v>
       </c>
       <c r="D38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <f t="shared" ca="1" si="0"/>
-        <v>126838408</v>
+        <f t="shared" si="0"/>
+        <v>140931564</v>
       </c>
       <c r="F38">
         <v>140931564</v>
       </c>
       <c r="G38" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -1817,18 +1788,17 @@
         <v>1</v>
       </c>
       <c r="D39" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <f t="shared" ca="1" si="0"/>
-        <v>25054500</v>
+        <f t="shared" si="0"/>
+        <v>31318125</v>
       </c>
       <c r="F39">
         <v>31318125</v>
       </c>
       <c r="G39" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -1842,18 +1812,17 @@
         <v>1</v>
       </c>
       <c r="D40" s="2">
-        <v>1</v>
-      </c>
-      <c r="E40">
-        <f t="shared" ca="1" si="0"/>
-        <v>42950572</v>
+        <v>2</v>
+      </c>
+      <c r="E40" s="7">
+        <f t="shared" si="0"/>
+        <v>53688215</v>
       </c>
       <c r="F40">
         <v>53688215</v>
       </c>
       <c r="G40" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -1867,17 +1836,16 @@
         <v>1</v>
       </c>
       <c r="D41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>17896071</v>
       </c>
       <c r="F41">
         <v>17896071</v>
       </c>
       <c r="G41" s="22">
-        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1892,17 +1860,16 @@
         <v>1</v>
       </c>
       <c r="D42" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>8948035</v>
       </c>
       <c r="F42">
         <v>8948035</v>
       </c>
       <c r="G42" s="22">
-        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1917,18 +1884,17 @@
         <v>1</v>
       </c>
       <c r="D43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -1942,18 +1908,17 @@
         <v>1</v>
       </c>
       <c r="D44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <f t="shared" ca="1" si="0"/>
-        <v>14810803</v>
+        <f t="shared" si="0"/>
+        <v>13464366</v>
       </c>
       <c r="F44">
         <v>13464366</v>
       </c>
       <c r="G44" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -1967,18 +1932,17 @@
         <v>1</v>
       </c>
       <c r="D45" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <f t="shared" ca="1" si="0"/>
-        <v>652504</v>
+        <f t="shared" si="0"/>
+        <v>725004</v>
       </c>
       <c r="F45">
         <v>725004</v>
       </c>
       <c r="G45" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -1992,18 +1956,17 @@
         <v>1</v>
       </c>
       <c r="D46" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F46">
         <v>0</v>
       </c>
       <c r="G46" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -2017,18 +1980,17 @@
         <v>1</v>
       </c>
       <c r="D47" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
       <c r="G47" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2042,18 +2004,17 @@
         <v>1</v>
       </c>
       <c r="D48" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <f t="shared" ca="1" si="0"/>
-        <v>62161440</v>
+        <f t="shared" si="0"/>
+        <v>56510400</v>
       </c>
       <c r="F48">
         <v>56510400</v>
       </c>
       <c r="G48" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2067,18 +2028,17 @@
         <v>1</v>
       </c>
       <c r="D49" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F49">
         <v>0</v>
       </c>
       <c r="G49" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2092,17 +2052,16 @@
         <v>1</v>
       </c>
       <c r="D50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>148533333</v>
       </c>
       <c r="F50">
         <v>148533333</v>
       </c>
       <c r="G50" s="22">
-        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2117,18 +2076,17 @@
         <v>1</v>
       </c>
       <c r="D51" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <f t="shared" ca="1" si="0"/>
-        <v>148530434</v>
+        <f t="shared" si="0"/>
+        <v>185663042</v>
       </c>
       <c r="F51">
         <v>185663042</v>
       </c>
       <c r="G51" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -2142,18 +2100,17 @@
         <v>1</v>
       </c>
       <c r="D52" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52">
-        <f t="shared" ca="1" si="0"/>
-        <v>3600000</v>
+        <f t="shared" si="0"/>
+        <v>4000000</v>
       </c>
       <c r="F52">
         <v>4000000</v>
       </c>
       <c r="G52" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2165,21 +2122,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFBA2FAA-95C5-423D-A8C0-3A912D67D407}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
       <c r="B1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -2191,8 +2158,16 @@
         <f>Medium_Capacity!C49*0.25</f>
         <v>3694295.5570033002</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <f ca="1">RAND()</f>
+        <v>0.84088922143042832</v>
+      </c>
+      <c r="E2">
+        <f ca="1">C2*D2</f>
+        <v>3106493.3146623955</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -2204,8 +2179,16 @@
         <f>Medium_Capacity!C50*0.25</f>
         <v>82819787.354738995</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <f t="shared" ref="D3:D18" ca="1" si="1">RAND()</f>
+        <v>0.77712599323032994</v>
+      </c>
+      <c r="E3">
+        <f ca="1">C3*D3</f>
+        <v>64361409.507176265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -2217,8 +2200,16 @@
         <f>Medium_Capacity!C51*0.25</f>
         <v>6513038.9940517964</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.32078089975437629</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E18" ca="1" si="2">C4*D4</f>
+        <v>2089258.5086472731</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -2230,8 +2221,16 @@
         <f>Medium_Capacity!C52*0.25</f>
         <v>1795007.6874129353</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.4590718880420751</v>
+      </c>
+      <c r="E5">
+        <f ca="1">C5*D5</f>
+        <v>824037.56811069523</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -2243,8 +2242,16 @@
         <f>Medium_Capacity!C53*0.25</f>
         <v>60870627.147684671</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.84448816763666579</v>
+      </c>
+      <c r="E6">
+        <f ca="1">C6*D6</f>
+        <v>51404524.382842913</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -2256,8 +2263,16 @@
         <f>Medium_Capacity!C54*0.25</f>
         <v>1601225.4899671054</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.14999176007729942</v>
+      </c>
+      <c r="E7">
+        <f ca="1">C7*D7</f>
+        <v>240170.62952080229</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -2269,8 +2284,16 @@
         <f>Medium_Capacity!C55*0.25</f>
         <v>15513537.879683325</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.75459933078209496</v>
+      </c>
+      <c r="E8">
+        <f t="shared" ca="1" si="2"/>
+        <v>11706505.302071717</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -2282,8 +2305,16 @@
         <f>Medium_Capacity!C56*0.25</f>
         <v>1456644.232631579</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.32551936313552587</v>
+      </c>
+      <c r="E9">
+        <f t="shared" ca="1" si="2"/>
+        <v>474165.90292126843</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -2295,8 +2326,16 @@
         <f>Medium_Capacity!C57*0.25</f>
         <v>63195503.325986847</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.50310844038834912</v>
+      </c>
+      <c r="E10">
+        <f t="shared" ca="1" si="2"/>
+        <v>31794191.117893972</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -2308,8 +2347,16 @@
         <f>Medium_Capacity!C58*0.25</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D11">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.83497031754189133</v>
+      </c>
+      <c r="E11">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -2321,8 +2368,16 @@
         <f>Medium_Capacity!C59*0.25</f>
         <v>20944761.71187168</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.46491136195553973</v>
+      </c>
+      <c r="E12">
+        <f t="shared" ca="1" si="2"/>
+        <v>9737457.6933005042</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -2334,8 +2389,16 @@
         <f>Medium_Capacity!C60*0.25</f>
         <v>109600740.51114175</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.14913708223485811</v>
+      </c>
+      <c r="E13">
+        <f t="shared" ca="1" si="2"/>
+        <v>16345534.650611492</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -2347,8 +2410,16 @@
         <f>Medium_Capacity!C61*0.25</f>
         <v>4747052.4303343054</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.4608516385956225E-2</v>
+      </c>
+      <c r="E14">
+        <f t="shared" ca="1" si="2"/>
+        <v>354170.53903359035</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -2360,8 +2431,16 @@
         <f>Medium_Capacity!C62*0.25</f>
         <v>14875638.036021562</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.52315551946276284</v>
+      </c>
+      <c r="E15">
+        <f t="shared" ca="1" si="2"/>
+        <v>7782272.1440748936</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -2373,8 +2452,16 @@
         <f>Medium_Capacity!C63*0.25</f>
         <v>231909.45848684199</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.24246553334762755</v>
+      </c>
+      <c r="E16">
+        <f t="shared" ca="1" si="2"/>
+        <v>56230.050540371631</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -2386,8 +2473,16 @@
         <f>Medium_Capacity!C64*0.25</f>
         <v>35619750.841946572</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D17">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.92868936918715628</v>
+      </c>
+      <c r="E17">
+        <f t="shared" ca="1" si="2"/>
+        <v>33079683.940011039</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -2398,6 +2493,14 @@
       <c r="C18">
         <f>Medium_Capacity!C65*0.25</f>
         <v>40200058.257479519</v>
+      </c>
+      <c r="D18">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.80965332066051199</v>
+      </c>
+      <c r="E18">
+        <f t="shared" ca="1" si="2"/>
+        <v>32548110.658914328</v>
       </c>
     </row>
   </sheetData>
@@ -2407,22 +2510,26 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C2B8D5-A351-43B6-AB72-03AAE787B34B}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2433,8 +2540,12 @@
       <c r="C2" s="19">
         <v>37210000</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <f ca="1">RAND()</f>
+        <v>0.43984288474233302</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2445,8 +2556,12 @@
       <c r="C3" s="19">
         <v>2610000</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <f t="shared" ref="D3:D13" ca="1" si="1">RAND()</f>
+        <v>0.81699506033651093</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2457,8 +2572,12 @@
       <c r="C4" s="19">
         <v>35730000</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.23702374055016484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -2469,8 +2588,12 @@
       <c r="C5" s="19">
         <v>5706000</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.22600741902720101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -2481,8 +2604,12 @@
       <c r="C6" s="19">
         <v>5777000</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.64513103699847951</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -2493,8 +2620,12 @@
       <c r="C7" s="19">
         <v>3207000</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.62478706774717307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -2505,8 +2636,12 @@
       <c r="C8" s="19">
         <v>2595000</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.2397338202516148E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -2517,8 +2652,12 @@
       <c r="C9" s="19">
         <v>3123000</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.46381474841430625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -2529,8 +2668,12 @@
       <c r="C10" s="19">
         <v>5222000</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.48721068682874735</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2541,8 +2684,12 @@
       <c r="C11" s="19">
         <v>1900000</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.75107324597581382</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2553,8 +2700,12 @@
       <c r="C12" s="19">
         <v>14250000</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.47792852007794884</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2564,6 +2715,10 @@
       </c>
       <c r="C13" s="19">
         <v>1608000</v>
+      </c>
+      <c r="D13">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.93275269406383443</v>
       </c>
     </row>
   </sheetData>
@@ -2674,7 +2829,7 @@
         <v>3.9562237561659988E-3</v>
       </c>
       <c r="D2" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A2)</f>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A2)</f>
         <v>0</v>
       </c>
       <c r="E2" s="15">
@@ -2682,7 +2837,7 @@
         <v>12600000</v>
       </c>
       <c r="F2" s="20">
-        <f ca="1">E2-D2</f>
+        <f>E2-D2</f>
         <v>12600000</v>
       </c>
       <c r="G2" s="5"/>
@@ -2754,16 +2909,16 @@
         <v>7.6298601011772823E-3</v>
       </c>
       <c r="D3" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A3)</f>
-        <v>14635997</v>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A3)</f>
+        <v>13305452</v>
       </c>
       <c r="E3" s="15">
         <f>VLOOKUP(Medium_Capacity!A3, Medium_Capacity!A2:A19:B2:B19, 2, FALSE)</f>
         <v>24300000</v>
       </c>
       <c r="F3" s="20">
-        <f t="shared" ref="F3:F18" ca="1" si="1">E3-D3</f>
-        <v>9664003</v>
+        <f t="shared" ref="F3:F18" si="1">E3-D3</f>
+        <v>10994548</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -2834,7 +2989,7 @@
         <v>2.5118880991530147E-3</v>
       </c>
       <c r="D4" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A4)</f>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A4)</f>
         <v>0</v>
       </c>
       <c r="E4" s="15">
@@ -2842,7 +2997,7 @@
         <v>8000000</v>
       </c>
       <c r="F4" s="20">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>8000000</v>
       </c>
       <c r="G4" s="5"/>
@@ -2914,7 +3069,7 @@
         <v>1.1303496446188567E-2</v>
       </c>
       <c r="D5" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A5)</f>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A5)</f>
         <v>0</v>
       </c>
       <c r="E5" s="15">
@@ -2922,7 +3077,7 @@
         <v>36000000</v>
       </c>
       <c r="F5" s="20">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>36000000</v>
       </c>
       <c r="G5" s="5"/>
@@ -2994,7 +3149,7 @@
         <v>2.6374825041106656E-3</v>
       </c>
       <c r="D6" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A6)</f>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A6)</f>
         <v>0</v>
       </c>
       <c r="E6" s="15">
@@ -3002,7 +3157,7 @@
         <v>8400000</v>
       </c>
       <c r="F6" s="20">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>8400000</v>
       </c>
       <c r="G6" s="5"/>
@@ -3074,16 +3229,16 @@
         <v>5.0269160584299713E-2</v>
       </c>
       <c r="D7" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A7)</f>
-        <v>124201806</v>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A7)</f>
+        <v>143967364</v>
       </c>
       <c r="E7" s="15">
         <f>VLOOKUP(Medium_Capacity!A7, Medium_Capacity!A6:A23:B6:B23, 2, FALSE)</f>
         <v>160100000</v>
       </c>
       <c r="F7" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>35898194</v>
+        <f t="shared" si="1"/>
+        <v>16132636</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -3154,16 +3309,16 @@
         <v>9.4195803718238052E-6</v>
       </c>
       <c r="D8" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A8)</f>
-        <v>30000</v>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A8)</f>
+        <v>0</v>
       </c>
       <c r="E8" s="15">
         <f>VLOOKUP(Medium_Capacity!A8, Medium_Capacity!A7:A24:B7:B24, 2, FALSE)</f>
         <v>30000</v>
       </c>
       <c r="F8" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>30000</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -3234,16 +3389,16 @@
         <v>0.51693087150507078</v>
       </c>
       <c r="D9" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A9)</f>
-        <v>501049488</v>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A9)</f>
+        <v>487344323</v>
       </c>
       <c r="E9" s="15">
         <f>VLOOKUP(Medium_Capacity!A9, Medium_Capacity!A8:A25:B8:B25, 2, FALSE)</f>
         <v>1646350000</v>
       </c>
       <c r="F9" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>1145300512</v>
+        <f t="shared" si="1"/>
+        <v>1159005677</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -3314,16 +3469,16 @@
         <v>2.5118880991530147E-3</v>
       </c>
       <c r="D10" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A10)</f>
-        <v>5400000</v>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A10)</f>
+        <v>6000000</v>
       </c>
       <c r="E10" s="15">
         <f>VLOOKUP(Medium_Capacity!A10, Medium_Capacity!A9:A26:B9:B26, 2, FALSE)</f>
         <v>8000000</v>
       </c>
       <c r="F10" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>2600000</v>
+        <f t="shared" si="1"/>
+        <v>2000000</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -3394,16 +3549,16 @@
         <v>1.9027552351084089E-2</v>
       </c>
       <c r="D11" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A11)</f>
-        <v>66152801</v>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A11)</f>
+        <v>58110013</v>
       </c>
       <c r="E11" s="15">
         <f>VLOOKUP(Medium_Capacity!A11, Medium_Capacity!A10:A27:B10:B27, 2, FALSE)</f>
         <v>60600000</v>
       </c>
       <c r="F11" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>-5552801</v>
+        <f t="shared" si="1"/>
+        <v>2489987</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -3474,16 +3629,16 @@
         <v>9.7335663842179328E-4</v>
       </c>
       <c r="D12" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A12)</f>
-        <v>3053115</v>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A12)</f>
+        <v>2907378</v>
       </c>
       <c r="E12" s="15">
         <f>VLOOKUP(Medium_Capacity!A12, Medium_Capacity!A11:A28:B11:B28, 2, FALSE)</f>
         <v>3100000</v>
       </c>
       <c r="F12" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>46885</v>
+        <f t="shared" si="1"/>
+        <v>192622</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -3554,7 +3709,7 @@
         <v>6.4367132540796004E-3</v>
       </c>
       <c r="D13" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A13)</f>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A13)</f>
         <v>8948035</v>
       </c>
       <c r="E13" s="15">
@@ -3562,7 +3717,7 @@
         <v>20500000</v>
       </c>
       <c r="F13" s="20">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>11551965</v>
       </c>
       <c r="G13" s="5"/>
@@ -3634,16 +3789,16 @@
         <v>1.8211188718859359E-3</v>
       </c>
       <c r="D14" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A14)</f>
-        <v>3600000</v>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A14)</f>
+        <v>4000000</v>
       </c>
       <c r="E14" s="15">
         <f>VLOOKUP(Medium_Capacity!A14, Medium_Capacity!A13:A30:B13:B30, 2, FALSE)</f>
         <v>5800000</v>
       </c>
       <c r="F14" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>2200000</v>
+        <f t="shared" si="1"/>
+        <v>1800000</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
@@ -3714,16 +3869,16 @@
         <v>3.6610769045155193E-2</v>
       </c>
       <c r="D15" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A15)</f>
-        <v>87588183</v>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A15)</f>
+        <v>86957885</v>
       </c>
       <c r="E15" s="15">
         <f>VLOOKUP(Medium_Capacity!A15, Medium_Capacity!A14:A31:B14:B31, 2, FALSE)</f>
         <v>116600000</v>
       </c>
       <c r="F15" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>29011817</v>
+        <f t="shared" si="1"/>
+        <v>29642115</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
@@ -3794,16 +3949,16 @@
         <v>3.2842936896425673E-2</v>
       </c>
       <c r="D16" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A16)</f>
-        <v>125503191</v>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A16)</f>
+        <v>104585992</v>
       </c>
       <c r="E16" s="15">
         <f>VLOOKUP(Medium_Capacity!A16, Medium_Capacity!A15:A32:B15:B32, 2, FALSE)</f>
         <v>104600000</v>
       </c>
       <c r="F16" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>-20903191</v>
+        <f t="shared" si="1"/>
+        <v>14008</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
@@ -3874,16 +4029,16 @@
         <v>0.30437026926105981</v>
       </c>
       <c r="D17" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A17)</f>
-        <v>494157473</v>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A17)</f>
+        <v>487523499</v>
       </c>
       <c r="E17" s="15">
         <f>VLOOKUP(Medium_Capacity!A17, Medium_Capacity!A16:A33:B16:B33, 2, FALSE)</f>
         <v>969375250</v>
       </c>
       <c r="F17" s="20">
-        <f ca="1">E17-D17</f>
-        <v>475217777</v>
+        <f>E17-D17</f>
+        <v>481851751</v>
       </c>
       <c r="J17">
         <f>VLOOKUP(Q_start!B17,Medium_Capacity!$B$30:$C$46,2)</f>
@@ -3951,7 +4106,7 @@
         <v>1.5699300619706342E-4</v>
       </c>
       <c r="D18" s="16">
-        <f ca="1">SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A18)</f>
+        <f>SUMIFS(Q_start!E:E, Q_start!B:B, Medium_Capacity!A18)</f>
         <v>0</v>
       </c>
       <c r="E18" s="15">
@@ -3959,7 +4114,7 @@
         <v>500000</v>
       </c>
       <c r="F18" s="20">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>500000</v>
       </c>
       <c r="G18" s="8"/>

--- a/Starting_point.xlsx
+++ b/Starting_point.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="963" documentId="13_ncr:1_{30A8FEE2-BE8F-4FE6-A73D-C8D61511F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF66EB9F-3A1B-4FC0-882C-92AC0AAADD8E}"/>
+  <xr:revisionPtr revIDLastSave="968" documentId="13_ncr:1_{30A8FEE2-BE8F-4FE6-A73D-C8D61511F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A360C964-A214-4EAB-82C3-2B884BE69F4F}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -387,6 +387,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -674,7 +678,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -685,7 +689,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -696,7 +700,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -707,7 +711,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -718,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -729,7 +733,7 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -740,7 +744,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -751,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -762,7 +766,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -773,7 +777,7 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -784,7 +788,7 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -795,7 +799,7 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +852,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <f>ROUND(F2*G2,0)</f>
@@ -872,7 +876,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <f>ROUND(F3*G3,0)</f>
@@ -896,7 +900,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f t="shared" ref="E4:E52" si="0">ROUND(F4*G4,0)</f>
@@ -923,7 +927,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="7">
         <f>ROUND(F5*G5,0)</f>
@@ -950,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
@@ -977,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
@@ -1004,7 +1008,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
@@ -1031,7 +1035,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
@@ -1058,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
@@ -1085,7 +1089,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
@@ -1109,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
@@ -1133,7 +1137,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
@@ -1157,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
@@ -1181,7 +1185,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <f t="shared" si="0"/>
@@ -1205,7 +1209,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16">
         <f t="shared" si="0"/>
@@ -1232,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <f t="shared" si="0"/>
@@ -1257,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <f t="shared" si="0"/>
@@ -1282,7 +1286,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <f t="shared" si="0"/>
@@ -1307,7 +1311,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20">
         <f t="shared" si="0"/>
@@ -1332,7 +1336,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <f t="shared" si="0"/>
@@ -1356,7 +1360,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <f t="shared" si="0"/>
@@ -1381,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <f t="shared" si="0"/>
@@ -1406,7 +1410,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <f t="shared" si="0"/>
@@ -1432,7 +1436,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
         <f t="shared" si="0"/>
@@ -1458,7 +1462,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <f t="shared" si="0"/>
@@ -1485,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27">
         <f t="shared" si="0"/>
@@ -1512,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <f t="shared" si="0"/>
@@ -1539,7 +1543,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29">
         <f t="shared" si="0"/>
@@ -1565,7 +1569,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30">
         <f t="shared" si="0"/>
@@ -1589,7 +1593,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31">
         <f t="shared" si="0"/>
@@ -1617,7 +1621,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32">
         <f t="shared" si="0"/>
@@ -1641,7 +1645,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33">
         <f t="shared" si="0"/>
@@ -1665,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34">
         <f t="shared" si="0"/>
@@ -1689,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35">
         <f t="shared" si="0"/>
@@ -1714,7 +1718,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36">
         <f t="shared" si="0"/>
@@ -1739,7 +1743,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37">
         <f t="shared" si="0"/>
@@ -1764,7 +1768,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38">
         <f t="shared" si="0"/>
@@ -1788,7 +1792,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39">
         <f t="shared" si="0"/>
@@ -1812,7 +1816,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="7">
         <f t="shared" si="0"/>
@@ -1836,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41">
         <f t="shared" si="0"/>
@@ -1860,7 +1864,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42">
         <f t="shared" si="0"/>
@@ -1884,7 +1888,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43">
         <f t="shared" si="0"/>
@@ -1908,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44">
         <f t="shared" si="0"/>
@@ -1932,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45">
         <f t="shared" si="0"/>
@@ -1956,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46">
         <f t="shared" si="0"/>
@@ -1980,7 +1984,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47">
         <f t="shared" si="0"/>
@@ -2004,7 +2008,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48">
         <f t="shared" si="0"/>
@@ -2028,7 +2032,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49">
         <f t="shared" si="0"/>
@@ -2052,7 +2056,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50">
         <f t="shared" si="0"/>
@@ -2076,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51">
         <f t="shared" si="0"/>
@@ -2100,7 +2104,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52">
         <f t="shared" si="0"/>
@@ -2160,11 +2164,11 @@
       </c>
       <c r="D2">
         <f ca="1">RAND()</f>
-        <v>0.84088922143042832</v>
+        <v>0.27035127248198476</v>
       </c>
       <c r="E2">
         <f ca="1">C2*D2</f>
-        <v>3106493.3146623955</v>
+        <v>998757.50476038491</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2181,11 +2185,11 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D18" ca="1" si="1">RAND()</f>
-        <v>0.77712599323032994</v>
+        <v>0.82374750869202262</v>
       </c>
       <c r="E3">
         <f ca="1">C3*D3</f>
-        <v>64361409.507176265</v>
+        <v>68222593.503869325</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2202,11 +2206,11 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="1"/>
-        <v>0.32078089975437629</v>
+        <v>0.58197216677238695</v>
       </c>
       <c r="E4">
         <f t="shared" ref="E4:E18" ca="1" si="2">C4*D4</f>
-        <v>2089258.5086472731</v>
+        <v>3790407.4156413712</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2223,11 +2227,11 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="1"/>
-        <v>0.4590718880420751</v>
+        <v>0.24365099253651057</v>
       </c>
       <c r="E5">
         <f ca="1">C5*D5</f>
-        <v>824037.56811069523</v>
+        <v>437355.4046488282</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2244,11 +2248,11 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84448816763666579</v>
+        <v>0.77603886295108393</v>
       </c>
       <c r="E6">
         <f ca="1">C6*D6</f>
-        <v>51404524.382842913</v>
+        <v>47237972.278808594</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2265,11 +2269,11 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="1"/>
-        <v>0.14999176007729942</v>
+        <v>0.83977854107809502</v>
       </c>
       <c r="E7">
         <f ca="1">C7*D7</f>
-        <v>240170.62952080229</v>
+        <v>1344674.8059016336</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2286,11 +2290,11 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75459933078209496</v>
+        <v>0.78407395795504209</v>
       </c>
       <c r="E8">
         <f t="shared" ca="1" si="2"/>
-        <v>11706505.302071717</v>
+        <v>12163761.047208777</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2307,11 +2311,11 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="1"/>
-        <v>0.32551936313552587</v>
+        <v>0.89335614837525301</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="2"/>
-        <v>474165.90292126843</v>
+        <v>1301302.0812167735</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2328,11 +2332,11 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.50310844038834912</v>
+        <v>0.93580901309007414</v>
       </c>
       <c r="E10">
         <f t="shared" ca="1" si="2"/>
-        <v>31794191.117893972</v>
+        <v>59138921.59922225</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2349,7 +2353,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="1"/>
-        <v>0.83497031754189133</v>
+        <v>0.31293332030954568</v>
       </c>
       <c r="E11">
         <f t="shared" ca="1" si="2"/>
@@ -2370,11 +2374,11 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="1"/>
-        <v>0.46491136195553973</v>
+        <v>0.19736390364392531</v>
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="2"/>
-        <v>9737457.6933005042</v>
+        <v>4133739.9323468185</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2391,11 +2395,11 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="1"/>
-        <v>0.14913708223485811</v>
+        <v>0.45176729690594974</v>
       </c>
       <c r="E13">
         <f t="shared" ca="1" si="2"/>
-        <v>16345534.650611492</v>
+        <v>49514030.279608928</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2412,11 +2416,11 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="1"/>
-        <v>7.4608516385956225E-2</v>
+        <v>0.98482961664104418</v>
       </c>
       <c r="E14">
         <f t="shared" ca="1" si="2"/>
-        <v>354170.53903359035</v>
+        <v>4675037.8251410713</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2433,11 +2437,11 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="1"/>
-        <v>0.52315551946276284</v>
+        <v>0.43868478702599667</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="2"/>
-        <v>7782272.1440748936</v>
+        <v>6525716.1037079347</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2454,11 +2458,11 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="1"/>
-        <v>0.24246553334762755</v>
+        <v>1.5070613982824055E-2</v>
       </c>
       <c r="E16">
         <f t="shared" ca="1" si="2"/>
-        <v>56230.050540371631</v>
+        <v>3495.0179278209557</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2475,11 +2479,11 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92868936918715628</v>
+        <v>0.18962409232298427</v>
       </c>
       <c r="E17">
         <f t="shared" ca="1" si="2"/>
-        <v>33079683.940011039</v>
+        <v>6754362.9221749734</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2496,11 +2500,11 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="1"/>
-        <v>0.80965332066051199</v>
+        <v>0.9577469847529797</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="2"/>
-        <v>32548110.658914328</v>
+        <v>38501484.582995132</v>
       </c>
     </row>
   </sheetData>
@@ -2542,7 +2546,7 @@
       </c>
       <c r="D2">
         <f ca="1">RAND()</f>
-        <v>0.43984288474233302</v>
+        <v>0.89426960692987123</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2558,7 +2562,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D13" ca="1" si="1">RAND()</f>
-        <v>0.81699506033651093</v>
+        <v>0.14213996265432316</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2574,7 +2578,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="1"/>
-        <v>0.23702374055016484</v>
+        <v>8.6255816151831533E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2590,7 +2594,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="1"/>
-        <v>0.22600741902720101</v>
+        <v>0.37914838496360848</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2606,7 +2610,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="1"/>
-        <v>0.64513103699847951</v>
+        <v>1.7858633285423586E-3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2622,7 +2626,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="1"/>
-        <v>0.62478706774717307</v>
+        <v>0.78940326849705678</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2638,7 +2642,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="1"/>
-        <v>7.2397338202516148E-2</v>
+        <v>0.56321705168496394</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2654,7 +2658,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="1"/>
-        <v>0.46381474841430625</v>
+        <v>0.39486012355704825</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2670,7 +2674,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="1"/>
-        <v>0.48721068682874735</v>
+        <v>0.98304633444705702</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2686,7 +2690,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75107324597581382</v>
+        <v>0.32696787781713776</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2702,7 +2706,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="1"/>
-        <v>0.47792852007794884</v>
+        <v>0.76070442003430705</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2718,7 +2722,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93275269406383443</v>
+        <v>0.63249786137992137</v>
       </c>
     </row>
   </sheetData>

--- a/Starting_point.xlsx
+++ b/Starting_point.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fthcn\Desktop\Vaccine_Tender_Scheduling_Problem\Julia_Files\Github\Github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A8FEE2-BE8F-4FE6-A73D-C8D61511F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -153,7 +153,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="173" formatCode="0.000E+00"/>
+    <numFmt numFmtId="164" formatCode="0.000E+00"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -225,7 +225,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -510,9 +510,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942AD6D9-E2BE-4540-AD66-B6783F716305}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -523,7 +523,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,7 +534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -545,7 +545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -556,7 +556,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -567,7 +567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -578,7 +578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -589,7 +589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -600,7 +600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -611,7 +611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -622,7 +622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -633,7 +633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -663,15 +663,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86710C76-81AC-48E5-8A5F-29B3CE6BD5DC}">
   <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="8.85546875" style="2"/>
     <col min="2" max="2" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.88671875" style="2"/>
-    <col min="5" max="5" width="16.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.85546875" style="2"/>
+    <col min="5" max="5" width="16.140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -688,7 +688,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>13299464</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -722,7 +722,7 @@
         <v>12505034</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -739,7 +739,7 @@
         <v>13547121</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -756,7 +756,7 @@
         <v>6547121</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -773,7 +773,7 @@
         <v>90279149</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
@@ -790,7 +790,7 @@
         <v>180177056</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -807,7 +807,7 @@
         <v>13305452</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -824,7 +824,7 @@
         <v>8948035</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -841,7 +841,7 @@
         <v>140931564</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
@@ -858,7 +858,7 @@
         <v>17896071</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -875,7 +875,7 @@
         <v>31318125</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
@@ -892,7 +892,7 @@
         <v>53688215</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>43365104</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -926,7 +926,7 @@
         <v>40213942</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
@@ -943,7 +943,7 @@
         <v>219201481</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>34</v>
       </c>
@@ -960,7 +960,7 @@
         <v>61220888</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
@@ -977,7 +977,7 @@
         <v>84680592</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -994,7 +994,7 @@
         <v>3625021</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>13464366</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>5390769</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>10</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>56510400</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>13</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>185663042</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>13</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>13</v>
       </c>
@@ -1138,9 +1138,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFBA2FAA-95C5-423D-A8C0-3A912D67D407}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>12542</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>7598</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>14598</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1188,13 +1188,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C2B8D5-A351-43B6-AB72-03AAE787B34B}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>37210000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>2610000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>35730000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>5706000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>5777000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>3207000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>2595000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>3123000</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>5222000</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>1900000</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>14250000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
